--- a/sampleprojects/TaxReturn/excel/states/OR.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OR.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $5,495 std ded, 9.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 5495.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 5495.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $4,415 std ded, 9.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 4415.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 4415.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
   </si>
   <si>
     <t>Default (Single/MFS): $2,745 std ded, 9.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 2745.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 2745.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.099</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/OR.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OR.xlsx
@@ -215,7 +215,7 @@
     <t>1991-10-01</t>
   </si>
   <si>
-    <t>OR military retirement: Service before this date is exempt, after is taxable (2025). Source: MOAA State Report Card</t>
+    <t>Oregon federal pension subtraction, Schedule OR-ASC code 307 (ORS 316.680(1)(e); 2025 Publication OR-17 p. 73): only the share of a federal pension, including military retired pay, earned by service or points before October 1, 1991 is subtracted (months before over total months, rounded to three places). Oregon has no other military retirement subtraction for 2025; without service dates in the data model the rules subtract nothing (#1330).</t>
   </si>
   <si>
     <t>or_national_guard_subtraction_limit</t>
